--- a/testdata/purchase_details.xlsx
+++ b/testdata/purchase_details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PlaywrightTS_DemoblazeProject\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C441DF-4E08-4A5B-93C2-942B4FA3B70D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5838C6-BC38-48DF-B367-5BF522C00CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3660" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{ECC864F3-9109-4E80-BFC1-F5F782CA700A}"/>
   </bookViews>
@@ -92,7 +92,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -435,42 +435,42 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>47885412486</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
+      <c r="E2" s="1">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1">
         <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>25885202486</v>
       </c>
       <c r="E3" s="1">
-        <v>8</v>
-      </c>
-      <c r="F3">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1">
         <v>30</v>
       </c>
     </row>
